--- a/data/trans_orig/P37A$vacunapreferencia-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P37A$vacunapreferencia-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14637</t>
+          <t>15209</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34328</t>
+          <t>34730</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3741</t>
+          <t>3966</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16387</t>
+          <t>15907</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21871</t>
+          <t>22232</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44027</t>
+          <t>45537</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,83%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>439448</t>
+          <t>439046</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>459139</t>
+          <t>458567</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>290293</t>
+          <t>290773</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>302939</t>
+          <t>302714</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>736430</t>
+          <t>734920</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>758586</t>
+          <t>758225</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,15%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3827</t>
+          <t>3917</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17778</t>
+          <t>17882</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,47 +1091,47 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4,87%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>8171</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>3862</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>16695</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>2,2%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
           <t>1,04%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4,84%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>8171</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>3380</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>16251</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2,2%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,91%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9837</t>
+          <t>9300</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27793</t>
+          <t>28036</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>349156</t>
+          <t>349052</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>363107</t>
+          <t>363017</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,49 +1204,49 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
+          <t>98,93%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>356</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>363694</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>355170</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>368003</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>97,8%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>95,51%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
           <t>98,96%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>356</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>363694</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>355614</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>368485</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>97,8%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>95,63%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,09%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>698</t>
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>711006</t>
+          <t>710763</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>728962</t>
+          <t>729499</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,74%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8763</t>
+          <t>9098</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24982</t>
+          <t>23861</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1538</t>
+          <t>1780</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10356</t>
+          <t>10197</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12858</t>
+          <t>13042</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29269</t>
+          <t>29509</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>517407</t>
+          <t>518528</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>533626</t>
+          <t>533291</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>157426</t>
+          <t>157585</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>166244</t>
+          <t>166002</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>680902</t>
+          <t>680662</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>697313</t>
+          <t>697129</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,16%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19748</t>
+          <t>19419</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41818</t>
+          <t>43292</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12222</t>
+          <t>11795</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30259</t>
+          <t>32295</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>37974</t>
+          <t>37382</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>66652</t>
+          <t>67997</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1196516</t>
+          <t>1195042</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1218586</t>
+          <t>1218915</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>684026</t>
+          <t>681990</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>702063</t>
+          <t>702490</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1885968</t>
+          <t>1884623</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1914646</t>
+          <t>1915238</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,09%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2988</t>
+          <t>3707</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16193</t>
+          <t>16789</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4194</t>
+          <t>4709</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18374</t>
+          <t>18183</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10410</t>
+          <t>10092</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28062</t>
+          <t>29084</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>334362</t>
+          <t>333766</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>347567</t>
+          <t>346848</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>550378</t>
+          <t>550569</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>564558</t>
+          <t>564043</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>891245</t>
+          <t>890223</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>908897</t>
+          <t>909215</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,9%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>1958</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12254</t>
+          <t>12262</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>25259</t>
+          <t>25461</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>49459</t>
+          <t>47871</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>29196</t>
+          <t>29461</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>53393</t>
+          <t>54949</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>285947</t>
+          <t>285939</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>296196</t>
+          <t>296243</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1199301</t>
+          <t>1200889</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1223501</t>
+          <t>1223299</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1493567</t>
+          <t>1492011</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1517764</t>
+          <t>1517499</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,1%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>74127</t>
+          <t>74921</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>112167</t>
+          <t>112407</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>67098</t>
+          <t>68272</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>107651</t>
+          <t>105476</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>152203</t>
+          <t>149770</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>206449</t>
+          <t>206136</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3158023</t>
+          <t>3157783</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3196063</t>
+          <t>3195269</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3270473</t>
+          <t>3272648</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3311026</t>
+          <t>3309852</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6441865</t>
+          <t>6442178</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6496111</t>
+          <t>6498544</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,75%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6208</t>
+          <t>7001</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21700</t>
+          <t>21103</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14601</t>
+          <t>14149</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11221</t>
+          <t>10403</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29107</t>
+          <t>28458</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>415511</t>
+          <t>416108</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>431003</t>
+          <t>430210</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>299853</t>
+          <t>300305</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>312427</t>
+          <t>312395</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>722558</t>
+          <t>723207</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>740444</t>
+          <t>741262</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,62%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11298</t>
+          <t>12570</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30997</t>
+          <t>31319</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2543</t>
+          <t>2870</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12378</t>
+          <t>12566</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17091</t>
+          <t>16532</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>38245</t>
+          <t>38508</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,09%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>387800</t>
+          <t>387478</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>407499</t>
+          <t>406227</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>325633</t>
+          <t>325445</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>335468</t>
+          <t>335141</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>718563</t>
+          <t>718300</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>739717</t>
+          <t>740276</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,82%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12322</t>
+          <t>12103</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29248</t>
+          <t>29453</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>1964</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11238</t>
+          <t>12131</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15558</t>
+          <t>15387</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35733</t>
+          <t>35900</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,04%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>600167</t>
+          <t>599962</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>617093</t>
+          <t>617312</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>248891</t>
+          <t>247998</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>258154</t>
+          <t>258165</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>853811</t>
+          <t>853644</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>873986</t>
+          <t>874157</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,27%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28529</t>
+          <t>27470</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>55070</t>
+          <t>53357</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7164</t>
+          <t>7045</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22063</t>
+          <t>20973</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>39292</t>
+          <t>38717</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>68258</t>
+          <t>68559</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1103939</t>
+          <t>1105652</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1130480</t>
+          <t>1131539</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>744594</t>
+          <t>745684</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>759493</t>
+          <t>759612</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1857409</t>
+          <t>1857108</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1886375</t>
+          <t>1886950</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,99%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3990</t>
+          <t>4042</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15592</t>
+          <t>17216</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15335</t>
+          <t>15895</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>34779</t>
+          <t>35247</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>22473</t>
+          <t>22570</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>45786</t>
+          <t>45752</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>495004</t>
+          <t>493380</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>506606</t>
+          <t>506554</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>726743</t>
+          <t>726275</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>746187</t>
+          <t>745627</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1226332</t>
+          <t>1226366</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1249645</t>
+          <t>1249548</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2037</t>
+          <t>2792</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12746</t>
+          <t>12712</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8252</t>
+          <t>7429</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>25037</t>
+          <t>24006</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13046</t>
+          <t>12155</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>31256</t>
+          <t>32248</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>254136</t>
+          <t>254170</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>264845</t>
+          <t>264090</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1084314</t>
+          <t>1085345</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1101099</t>
+          <t>1101922</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1344977</t>
+          <t>1343985</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1363187</t>
+          <t>1364078</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,12%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>85395</t>
+          <t>84884</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>126289</t>
+          <t>125608</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>54143</t>
+          <t>52159</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>88656</t>
+          <t>85047</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>146785</t>
+          <t>149364</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>201203</t>
+          <t>202008</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3295621</t>
+          <t>3296302</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3336515</t>
+          <t>3337026</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3461469</t>
+          <t>3465078</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3495982</t>
+          <t>3497966</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6770832</t>
+          <t>6770027</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6825250</t>
+          <t>6822671</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,86%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3549</t>
+          <t>3180</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14728</t>
+          <t>14046</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3176</t>
+          <t>3134</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14870</t>
+          <t>14723</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8628</t>
+          <t>8945</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24292</t>
+          <t>24454</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>414364</t>
+          <t>415046</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>425543</t>
+          <t>425912</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>332185</t>
+          <t>332332</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>343879</t>
+          <t>343921</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>751855</t>
+          <t>751693</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>767519</t>
+          <t>767202</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,85%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1070</t>
+          <t>1520</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11623</t>
+          <t>11735</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2039</t>
+          <t>2047</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11680</t>
+          <t>12527</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4426</t>
+          <t>4659</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17879</t>
+          <t>17949</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>365604</t>
+          <t>365492</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>376157</t>
+          <t>375707</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>360593</t>
+          <t>359746</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>370234</t>
+          <t>370226</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>731621</t>
+          <t>731551</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>745074</t>
+          <t>744841</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6549,7 +6549,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,38%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4145</t>
+          <t>4083</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15154</t>
+          <t>14529</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9344</t>
+          <t>9110</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6744,7 +6744,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6977</t>
+          <t>7004</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20405</t>
+          <t>21152</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>506760</t>
+          <t>507385</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>517769</t>
+          <t>517831</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>156779</t>
+          <t>157013</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>165115</t>
+          <t>165106</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,7 +6852,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>667631</t>
+          <t>666884</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>681059</t>
+          <t>681032</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,98%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13126</t>
+          <t>13744</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30680</t>
+          <t>31641</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4221</t>
+          <t>3859</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17863</t>
+          <t>16619</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,47 +7082,47 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
+          <t>2,01%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>29803</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>20131</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>42644</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
           <t>2,16%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>29803</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>20432</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>42171</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>1,51%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1118958</t>
+          <t>1117997</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1136512</t>
+          <t>1135894</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>808013</t>
+          <t>809257</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>821655</t>
+          <t>822017</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,47 +7195,47 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
+          <t>97,99%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>99,53%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1872</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1945711</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>1932870</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>1955383</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>98,49%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>97,84%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,49%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1872</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1945711</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>1933343</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1955082</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>98,49%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>97,87%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,98%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5467</t>
+          <t>5570</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20081</t>
+          <t>20622</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4304</t>
+          <t>4110</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17750</t>
+          <t>19421</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12312</t>
+          <t>12239</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>31671</t>
+          <t>32305</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>600625</t>
+          <t>600084</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>615239</t>
+          <t>615136</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>720494</t>
+          <t>718823</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>733940</t>
+          <t>734134</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1327279</t>
+          <t>1326645</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1346638</t>
+          <t>1346711</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,1%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7723,7 +7723,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5897</t>
+          <t>6098</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18867</t>
+          <t>19208</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>43318</t>
+          <t>43355</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>21454</t>
+          <t>21218</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>43811</t>
+          <t>45219</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>281248</t>
+          <t>281047</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1038707</t>
+          <t>1038670</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1063158</t>
+          <t>1062817</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1325359</t>
+          <t>1323951</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1347716</t>
+          <t>1347952</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,45%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>41756</t>
+          <t>40923</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>72116</t>
+          <t>69266</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>48174</t>
+          <t>48688</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>81501</t>
+          <t>83146</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>98304</t>
+          <t>96240</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>143298</t>
+          <t>142950</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,7 +8146,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3313606</t>
+          <t>3316456</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3343966</t>
+          <t>3344799</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3450095</t>
+          <t>3448450</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3483422</t>
+          <t>3482908</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6774020</t>
+          <t>6774368</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6819014</t>
+          <t>6821078</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8264,7 +8264,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,61%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>52583</t>
+          <t>53560</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>39469</t>
+          <t>40336</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>68802</t>
+          <t>71429</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>49196</t>
+          <t>54300</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>39676</t>
+          <t>43069</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>61082</t>
+          <t>67485</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>101779</t>
+          <t>107860</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>85463</t>
+          <t>90446</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>121165</t>
+          <t>127491</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,27%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>452629</t>
+          <t>497058</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>436410</t>
+          <t>479189</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>465743</t>
+          <t>510282</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>398271</t>
+          <t>434111</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>386385</t>
+          <t>420926</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>407791</t>
+          <t>445342</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>850900</t>
+          <t>931169</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>831514</t>
+          <t>911538</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>867216</t>
+          <t>948583</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>91,3%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>46397</t>
+          <t>49803</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34331</t>
+          <t>35984</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>61296</t>
+          <t>64100</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>31636</t>
+          <t>34724</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22963</t>
+          <t>25065</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>41247</t>
+          <t>44448</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>78034</t>
+          <t>84527</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>64175</t>
+          <t>69637</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>94744</t>
+          <t>104932</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,58%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>405816</t>
+          <t>433409</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>390917</t>
+          <t>419112</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>417882</t>
+          <t>447228</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>350944</t>
+          <t>388419</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>341333</t>
+          <t>378695</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>359617</t>
+          <t>398078</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>756759</t>
+          <t>821828</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>740049</t>
+          <t>801423</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>770618</t>
+          <t>836718</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,32%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>33703</t>
+          <t>37180</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10857</t>
+          <t>26763</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>58661</t>
+          <t>50995</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>10223</t>
+          <t>11336</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6271</t>
+          <t>7234</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15733</t>
+          <t>17565</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>43926</t>
+          <t>48516</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18107</t>
+          <t>36902</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>67124</t>
+          <t>62352</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>9,46%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>634561</t>
+          <t>434432</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>609603</t>
+          <t>420617</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>657407</t>
+          <t>444849</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>89,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>156688</t>
+          <t>176161</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>151178</t>
+          <t>169932</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>160640</t>
+          <t>180263</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>791249</t>
+          <t>610593</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>768051</t>
+          <t>596757</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>817068</t>
+          <t>622207</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>94,4%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>85957</t>
+          <t>99466</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>69045</t>
+          <t>80462</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>106440</t>
+          <t>119462</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>60910</t>
+          <t>68222</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32294</t>
+          <t>55756</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>82808</t>
+          <t>82204</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>146867</t>
+          <t>167688</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>100495</t>
+          <t>144357</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>173796</t>
+          <t>195630</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>9,82%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>948862</t>
+          <t>1032377</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>928379</t>
+          <t>1012381</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>965774</t>
+          <t>1051381</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>917184</t>
+          <t>792989</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>895286</t>
+          <t>779007</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>945800</t>
+          <t>805455</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1866045</t>
+          <t>1825366</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1839116</t>
+          <t>1797424</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1912417</t>
+          <t>1848697</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>92,76%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>24503</t>
+          <t>27172</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15099</t>
+          <t>18179</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35107</t>
+          <t>38553</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>46726</t>
+          <t>52452</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>32876</t>
+          <t>41095</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>59380</t>
+          <t>64049</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>71229</t>
+          <t>79625</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>55687</t>
+          <t>65173</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>87257</t>
+          <t>96639</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,91%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>450543</t>
+          <t>540792</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>439939</t>
+          <t>529411</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>459947</t>
+          <t>549785</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>794609</t>
+          <t>778398</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>781955</t>
+          <t>766801</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>808459</t>
+          <t>789755</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1245152</t>
+          <t>1319189</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1229124</t>
+          <t>1302175</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1260694</t>
+          <t>1333641</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,34%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,7 +10348,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1025</t>
+          <t>940</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5533</t>
+          <t>4919</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>58853</t>
+          <t>63614</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>47597</t>
+          <t>52215</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>72875</t>
+          <t>78361</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>59878</t>
+          <t>64554</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>48062</t>
+          <t>52425</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>74242</t>
+          <t>78462</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,25%</t>
         </is>
       </c>
     </row>
@@ -10461,27 +10461,27 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>239482</t>
+          <t>236288</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>234974</t>
+          <t>232309</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>702518</t>
+          <t>780667</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>688496</t>
+          <t>765920</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>713774</t>
+          <t>792066</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>942000</t>
+          <t>1016955</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>927636</t>
+          <t>1003047</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>953816</t>
+          <t>1029084</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,15%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>244168</t>
+          <t>268121</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>189491</t>
+          <t>239779</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>280392</t>
+          <t>303141</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>257545</t>
+          <t>284649</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>213748</t>
+          <t>255020</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>294043</t>
+          <t>313081</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>501713</t>
+          <t>552770</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>431903</t>
+          <t>515114</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>551416</t>
+          <t>596594</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,43%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3131892</t>
+          <t>3174355</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3095668</t>
+          <t>3139335</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3186569</t>
+          <t>3202697</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3320213</t>
+          <t>3350744</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3283715</t>
+          <t>3322312</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3364010</t>
+          <t>3380373</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6452105</t>
+          <t>6525099</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6402402</t>
+          <t>6481275</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6521915</t>
+          <t>6562755</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>92,72%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
